--- a/artfynd/A 18731-2024 artfynd.xlsx
+++ b/artfynd/A 18731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721157</v>
       </c>
       <c r="B2" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129721149</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2024 artfynd.xlsx
+++ b/artfynd/A 18731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721157</v>
       </c>
       <c r="B2" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129721149</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2024 artfynd.xlsx
+++ b/artfynd/A 18731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721157</v>
       </c>
       <c r="B2" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129721149</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2024 artfynd.xlsx
+++ b/artfynd/A 18731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721157</v>
       </c>
       <c r="B2" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129721149</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2024 artfynd.xlsx
+++ b/artfynd/A 18731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721157</v>
       </c>
       <c r="B2" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129721149</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18731-2024 artfynd.xlsx
+++ b/artfynd/A 18731-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129721157</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129721149</v>
       </c>
       <c r="B3" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
